--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2022-01-30</t>
+          <t>2022-01-31</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2021-10-18</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2021-10-18</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2023-04-02</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8761,7 +8761,7 @@
           <t>1 | 3309呎 (4+房)
 $45941万
 $138,836/呎
-(21年-03月-02日)</t>
+(21年-03月-03日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -8823,7 +8823,7 @@
           <t>1 | 2886呎 (4+房)
 $27063万
 $93,775/呎
-(22年-06月-22日)</t>
+(22年-06月-23日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -8831,7 +8831,7 @@
           <t>2 | 2096呎 (4+房)
 $18080万
 $86,260/呎
-(23年-10月-24日)</t>
+(23年-10月-25日)</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
           <t>1 | 2886呎 (4+房)
 $25000万
 $86,625/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -8854,7 +8854,7 @@
           <t>2 | 2096呎 (4+房)
 $16952万
 $80,878/呎
-(21年-07月-15日)</t>
+(21年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
           <t>2 | 2096呎 (4+房)
 $17000万
 $81,107/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
           <t>1 | 2945呎 (4+房)
 $23854万
 $81,000/呎
-(21年-07月-01日)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -8900,7 +8900,7 @@
           <t>2 | 2096呎 (4+房)
 $16000万
 $76,336/呎
-(21年-09月-29日)</t>
+(21年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
           <t>1 | 2886呎 (4+房)
 $23280万
 $80,665/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -8923,7 +8923,7 @@
           <t>2 | 2096呎 (4+房)
 $15500万
 $73,950/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
           <t>1 | 2886呎 (4+房)
 $23146万
 $80,201/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -8946,7 +8946,7 @@
           <t>2 | 2154呎 (4+房)
 $15078万
 $70,000/呎
-(21年-04月-14日)</t>
+(21年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
           <t>1 | 2886呎 (4+房)
 $22971万
 $79,595/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -8969,7 +8969,7 @@
           <t>2 | 2096呎 (4+房)
 $14550万
 $69,418/呎
-(23年-03月-23日)</t>
+(23年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
           <t>1 | 2886呎 (4+房)
 $21035万
 $72,885/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -8992,7 +8992,7 @@
           <t>2 | 2096呎 (4+房)
 $13600万
 $64,885/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
           <t>1 | 2886呎 (4+房)
 $21800万
 $75,537/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9015,7 +9015,7 @@
           <t>2 | 2154呎 (4+房)
 $13300万
 $61,746/呎
-(22年-11月-15日)</t>
+(22年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
           <t>3 | 2664呎 (4+房)
 $34411万
 $129,169/呎
-(21年-05月-10日)</t>
+(21年-05月-11日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -9318,7 +9318,7 @@
           <t>3 | 2133呎 (4+房)
 $20000万
 $93,765/呎
-(21年-11月-23日)</t>
+(21年-11月-24日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -9326,7 +9326,7 @@
           <t>5 | 2109呎 (4+房)
 $18600万
 $88,193/呎
-(21年-11月-23日)</t>
+(21年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
           <t>3 | 2133呎 (4+房)
 $17680万
 $82,888/呎
-(22年-01月-06日)</t>
+(22年-01月-07日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9410,7 +9410,7 @@
           <t>3 | 2133呎 (4+房)
 $17200万
 $80,638/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9433,7 +9433,7 @@
           <t>3 | 2133呎 (4+房)
 $16780万
 $78,669/呎
-(22年-02月-28日)</t>
+(22年-03月-01日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9456,7 +9456,7 @@
           <t>3 | 2133呎 (4+房)
 $16200万
 $75,949/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9479,7 +9479,7 @@
           <t>3 | 2133呎 (4+房)
 $15600万
 $73,136/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -9502,7 +9502,7 @@
           <t>3 | 2133呎 (4+房)
 $15380万
 $72,105/呎
-(23年-05月-04日)</t>
+(23年-05月-05日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -9548,7 +9548,7 @@
           <t>3 | 2133呎 (4+房)
 $14800万
 $69,386/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -9732,7 +9732,7 @@
           <t>3 | 2065呎 (4+房)
 $12695万
 $61,477/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -9740,7 +9740,7 @@
           <t>5 | 2029呎 (4+房)
 $12560万
 $61,902/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
           <t>6 | 2927呎 (4+房)
 $37737万
 $128,927/呎
-(21年-04月-15日)</t>
+(21年-04月-16日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -9882,7 +9882,7 @@
           <t>6 | 2112呎 (4+房)
 $18150万
 $85,938/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -9890,7 +9890,7 @@
           <t>7 | 2256呎 (4+房)
 $20850万
 $92,420/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9905,7 @@
           <t>6 | 2112呎 (4+房)
 $19011万
 $90,014/呎
-(22年-06月-01日)</t>
+(22年-06月-02日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9913,7 +9913,7 @@
           <t>7 | 2256呎 (4+房)
 $20389万
 $90,376/呎
-(22年-06月-01日)</t>
+(22年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
           <t>6 | 2112呎 (4+房)
 $17200万
 $81,439/呎
-(21年-11月-15日)</t>
+(21年-11月-16日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9959,7 +9959,7 @@
           <t>7 | 2256呎 (4+房)
 $19038万
 $84,388/呎
-(21年-08月-15日)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
           <t>6 | 2112呎 (4+房)
 $16680万
 $78,977/呎
-(22年-01月-30日)</t>
+(22年-01月-31日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -9982,7 +9982,7 @@
           <t>7 | 2256呎 (4+房)
 $18523万
 $82,107/呎
-(21年-10月-20日)</t>
+(21年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
           <t>7 | 2256呎 (4+房)
 $18000万
 $79,787/呎
-(21年-10月-18日)</t>
+(21年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
           <t>6 | 2112呎 (4+房)
 $15930万
 $75,426/呎
-(21年-10月-11日)</t>
+(21年-10月-12日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -10028,7 +10028,7 @@
           <t>7 | 2256呎 (4+房)
 $17360万
 $76,950/呎
-(21年-10月-18日)</t>
+(21年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10043,7 @@
           <t>6 | 2112呎 (4+房)
 $15480万
 $73,295/呎
-(21年-09月-09日)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -10051,7 +10051,7 @@
           <t>7 | 2256呎 (4+房)
 $16800万
 $74,468/呎
-(21年-04月-26日)</t>
+(21年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
           <t>6 | 2112呎 (4+房)
 $14000万
 $66,288/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10097,7 +10097,7 @@
           <t>7 | 2256呎 (4+房)
 $16280万
 $72,163/呎
-(23年-04月-02日)</t>
+(23年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
           <t>6 | 2112呎 (4+房)
 $14400万
 $68,182/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -10120,7 +10120,7 @@
           <t>7 | 2256呎 (4+房)
 $15280万
 $67,730/呎
-(23年-03月-20日)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
           <t>6 | 2112呎 (4+房)
 $13600万
 $64,394/呎
-(23年-12月-11日)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10181,7 +10181,7 @@
           <t>6 | 2112呎 (4+房)
 $13080万
 $61,932/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -10189,7 +10189,7 @@
           <t>7 | 2256呎 (4+房)
 $14420万
 $63,918/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
           <t>6 | 2112呎 (4+房)
 $11700万
 $55,398/呎
-(24年-07月-11日)</t>
+(24年-07月-12日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -10235,7 +10235,7 @@
           <t>7 | 2256呎 (4+房)
 $13842万
 $61,357/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
           <t>6 | 2112呎 (4+房)
 $11500万
 $54,451/呎
-(24年-06月-11日)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10296,7 +10296,7 @@
           <t>6 | 2032呎 (4+房)
 $12630万
 $62,156/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10304,7 +10304,7 @@
           <t>7 | 2176呎 (4+房)
 $15430万
 $70,910/呎
-(21年-10月-21日)</t>
+(21年-10月-22日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,12 +126,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -209,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -275,9 +269,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7713,23 +7704,19 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>147600000</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>63731</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7738,12 +7725,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
@@ -7753,7 +7740,7 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9801,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9824,7 +9811,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -10161,12 +10148,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>7 | 2316呎 (4+房)
-招标单位
--
-(在售)</t>
+$14760万
+$63,731/呎
+(26年-08月-10日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +126,12 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -203,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -269,6 +275,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4712,7 +4721,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4722,12 +4731,12 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -4737,12 +4746,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4752,7 +4761,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9237,27 +9246,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -9507,12 +9516,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>3 | 2193呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">

--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,12 +126,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -209,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -275,9 +269,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4721,23 +4712,19 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>151000000</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>68855</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4746,12 +4733,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4761,7 +4748,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9233,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9256,7 +9243,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9516,12 +9503,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>3 | 2193呎 (4+房)
-招标单位
--
-(在售)</t>
+$15100万
+$68,855/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">

--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -2232,12 +2232,12 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>2316</v>
+        <v>2256</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7705,14 +7705,14 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
         <v>147600000</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>63731</v>
+        <v>65426</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -10146,10 +10146,10 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>7 | 2316呎 (4+房)
+          <t>7 | 2256呎 (4+房)
 $14760万
-$63,731/呎
-(26年-08月-10日)</t>
+$65,426/呎
+(26年-09月-01日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2193</v>
+        <v>2133</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4717,14 +4717,14 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
         <v>151000000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>68855</v>
+        <v>70792</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -9505,10 +9505,10 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>3 | 2193呎 (4+房)
+          <t>3 | 2133呎 (4+房)
 $15100万
-$68,855/呎
-(26年-08月-17日)</t>
+$70,792/呎
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
